--- a/research/traditional_assets/database/data/lithuania/lithuania_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_engineering_construction.xlsx
@@ -588,115 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.031</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E2">
+        <v>0.229</v>
       </c>
       <c r="G2">
-        <v>0.02174303683737646</v>
+        <v>-0.01019786910197869</v>
       </c>
       <c r="H2">
-        <v>0.02174303683737646</v>
+        <v>-0.01019786910197869</v>
       </c>
       <c r="I2">
-        <v>-0.01599281221922732</v>
+        <v>-0.007001522070015221</v>
       </c>
       <c r="J2">
-        <v>-0.01599281221922732</v>
+        <v>-0.006798752265602514</v>
       </c>
       <c r="K2">
-        <v>-0.57</v>
+        <v>5.7</v>
       </c>
       <c r="L2">
-        <v>-0.005121293800539084</v>
+        <v>0.04337899543378995</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0001162790697674419</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.0001754385964912281</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0001162790697674419</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.0001754385964912281</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>10.7</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="V2">
-        <v>1.18232044198895</v>
+        <v>1.148837209302326</v>
       </c>
       <c r="W2">
-        <v>-0.01623931623931624</v>
+        <v>0.19</v>
       </c>
       <c r="X2">
-        <v>0.2067900052572896</v>
+        <v>0.2020094139688288</v>
       </c>
       <c r="Y2">
-        <v>-0.2230293214966058</v>
+        <v>-0.01200941396882876</v>
       </c>
       <c r="Z2">
-        <v>2.727941176470588</v>
+        <v>3.158653846153847</v>
       </c>
       <c r="AA2">
-        <v>-0.04362745098039215</v>
+        <v>-0.02147490499279256</v>
       </c>
       <c r="AB2">
-        <v>0.09455449927163084</v>
+        <v>0.0845361836443685</v>
       </c>
       <c r="AC2">
-        <v>-0.138181950252023</v>
+        <v>-0.1060110886371611</v>
       </c>
       <c r="AD2">
-        <v>22.3</v>
+        <v>26.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>22.3</v>
+        <v>26.3</v>
       </c>
       <c r="AG2">
-        <v>11.6</v>
+        <v>16.42</v>
       </c>
       <c r="AH2">
-        <v>0.7113237639553429</v>
+        <v>0.7535816618911175</v>
       </c>
       <c r="AI2">
-        <v>0.416044776119403</v>
+        <v>0.4361525704809287</v>
       </c>
       <c r="AJ2">
-        <v>0.5617433414043583</v>
+        <v>0.6562749800159872</v>
       </c>
       <c r="AK2">
-        <v>0.2703962703962704</v>
+        <v>0.3256644188813963</v>
       </c>
       <c r="AL2">
-        <v>0.249</v>
+        <v>1.28</v>
       </c>
       <c r="AM2">
-        <v>0.223</v>
+        <v>1.28</v>
       </c>
       <c r="AN2">
-        <v>-29.07431551499348</v>
+        <v>58.31485587583148</v>
       </c>
       <c r="AO2">
-        <v>-7.14859437751004</v>
+        <v>-0.71875</v>
       </c>
       <c r="AP2">
-        <v>-15.1238591916558</v>
+        <v>36.4079822616408</v>
       </c>
       <c r="AQ2">
-        <v>-7.982062780269058</v>
+        <v>-0.71875</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.031</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.229</v>
       </c>
       <c r="G3">
-        <v>0.02174303683737646</v>
+        <v>-0.01019786910197869</v>
       </c>
       <c r="H3">
-        <v>0.02174303683737646</v>
+        <v>-0.01019786910197869</v>
       </c>
       <c r="I3">
-        <v>-0.01599281221922732</v>
+        <v>-0.007001522070015221</v>
       </c>
       <c r="J3">
-        <v>-0.01599281221922732</v>
+        <v>-0.006798752265602514</v>
       </c>
       <c r="K3">
-        <v>-0.57</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
-        <v>-0.005121293800539084</v>
+        <v>0.04337899543378995</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0001162790697674419</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.0001754385964912281</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0001162790697674419</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.0001754385964912281</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>10.7</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="V3">
-        <v>1.18232044198895</v>
+        <v>1.148837209302326</v>
       </c>
       <c r="W3">
-        <v>-0.01623931623931624</v>
+        <v>0.19</v>
       </c>
       <c r="X3">
-        <v>0.2067900052572896</v>
+        <v>0.2020094139688288</v>
       </c>
       <c r="Y3">
-        <v>-0.2230293214966058</v>
+        <v>-0.01200941396882876</v>
       </c>
       <c r="Z3">
-        <v>2.727941176470588</v>
+        <v>3.158653846153847</v>
       </c>
       <c r="AA3">
-        <v>-0.04362745098039215</v>
+        <v>-0.02147490499279256</v>
       </c>
       <c r="AB3">
-        <v>0.09455449927163084</v>
+        <v>0.0845361836443685</v>
       </c>
       <c r="AC3">
-        <v>-0.138181950252023</v>
+        <v>-0.1060110886371611</v>
       </c>
       <c r="AD3">
-        <v>22.3</v>
+        <v>26.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>22.3</v>
+        <v>26.3</v>
       </c>
       <c r="AG3">
-        <v>11.6</v>
+        <v>16.42</v>
       </c>
       <c r="AH3">
-        <v>0.7113237639553429</v>
+        <v>0.7535816618911175</v>
       </c>
       <c r="AI3">
-        <v>0.416044776119403</v>
+        <v>0.4361525704809287</v>
       </c>
       <c r="AJ3">
-        <v>0.5617433414043583</v>
+        <v>0.6562749800159872</v>
       </c>
       <c r="AK3">
-        <v>0.2703962703962704</v>
+        <v>0.3256644188813963</v>
       </c>
       <c r="AL3">
-        <v>0.249</v>
+        <v>1.28</v>
       </c>
       <c r="AM3">
-        <v>0.223</v>
+        <v>1.28</v>
       </c>
       <c r="AN3">
-        <v>-29.07431551499348</v>
+        <v>58.31485587583148</v>
       </c>
       <c r="AO3">
-        <v>-7.14859437751004</v>
+        <v>-0.71875</v>
       </c>
       <c r="AP3">
-        <v>-15.1238591916558</v>
+        <v>36.4079822616408</v>
       </c>
       <c r="AQ3">
-        <v>-7.982062780269058</v>
+        <v>-0.71875</v>
       </c>
     </row>
   </sheetData>
